--- a/data/trans_camb/P1408-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1408-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>-0,87</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-0,69</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; -0,32</t>
+          <t>-3,52; -0,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,45</t>
+          <t>-2,66; 1,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,46</t>
+          <t>-2,68; 0,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; -0,05</t>
+          <t>-3,1; 0,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,33</t>
+          <t>-2,83; 0,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,88</t>
+          <t>-2,04; 1,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,46</t>
+          <t>-2,61; -0,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,46</t>
+          <t>-2,06; 0,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,29</t>
+          <t>-2,04; 0,43</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-47,74%</t>
+          <t>-42,32%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-21,63%</t>
+          <t>-26,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-38,86%</t>
+          <t>-37,36%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,69</t>
+          <t>-100,0; 16,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,82; 155,03</t>
+          <t>-84,25; 112,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,23; 72,15</t>
+          <t>-80,29; 89,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,24; 171,24</t>
+          <t>-77,3; 309,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-95,16; -12,0</t>
+          <t>-95,21; -29,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-79,72; 47,15</t>
+          <t>-79,4; 54,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,35; 27,61</t>
+          <t>-72,39; 41,16</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,98</t>
+          <t>-3,01</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-1,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,21; -0,31</t>
+          <t>-5,36; -0,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,05; -2,06</t>
+          <t>-6,18; -2,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -1,03</t>
+          <t>-5,31; -1,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,23</t>
+          <t>-3,29; -0,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,59</t>
+          <t>-2,9; 0,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,2</t>
+          <t>-2,07; 1,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,55</t>
+          <t>-3,64; -0,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -1,21</t>
+          <t>-3,75; -1,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; -0,3</t>
+          <t>-3,16; -0,41</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-70,87%</t>
+          <t>-71,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-10,11%</t>
+          <t>-14,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-53,39%</t>
+          <t>-55,09%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-94,98; 25,76</t>
+          <t>-95,58; 2,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -51,21</t>
+          <t>-100,0; -54,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,88; -31,2</t>
+          <t>-89,17; -32,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 102,6</t>
+          <t>-100,0; 109,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,6</t>
+          <t>-100,0; 131,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,87; 165,32</t>
+          <t>-67,45; 181,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-91,96; -5,84</t>
+          <t>-92,71; -4,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,91; -43,11</t>
+          <t>-95,38; -44,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-76,43; -9,87</t>
+          <t>-75,55; -15,86</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,49</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-0,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 0,44</t>
+          <t>-4,25; 0,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -0,51</t>
+          <t>-4,74; -0,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; -0,28</t>
+          <t>-4,01; 0,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -0,04</t>
+          <t>-6,66; 0,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -1,4</t>
+          <t>-7,79; -1,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,74</t>
+          <t>-3,82; 4,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; -0,26</t>
+          <t>-4,13; -0,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -1,03</t>
+          <t>-4,73; -1,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,09</t>
+          <t>-2,92; 1,15</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-53,67%</t>
+          <t>-32,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-41,94%</t>
+          <t>-22,19%</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,87; 18,25</t>
+          <t>-71,1; 22,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,77; -6,96</t>
+          <t>-78,72; -9,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,25; -7,1</t>
+          <t>-64,76; 33,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-94,82; 68,47</t>
+          <t>-100,0; 57,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,71; 221,82</t>
+          <t>-62,85; 302,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,51; -4,14</t>
+          <t>-72,47; -8,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,77; -23,68</t>
+          <t>-84,29; -27,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-80,02; -0,21</t>
+          <t>-52,27; 37,35</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,36</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-1,38</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-1,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,26</t>
+          <t>-2,92; 0,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,41; -0,48</t>
+          <t>-3,5; -0,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,06</t>
+          <t>-3,07; 0,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -1,36</t>
+          <t>-4,08; -1,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,45</t>
+          <t>-3,53; -0,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,36</t>
+          <t>-3,15; -0,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,78</t>
+          <t>-2,9; -0,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; -1,05</t>
+          <t>-3,15; -0,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,59</t>
+          <t>-2,7; -0,41</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-29,58%</t>
+          <t>-31,68%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-54,3%</t>
+          <t>-44,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-41,9%</t>
+          <t>-37,49%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-53,6; 9,45</t>
+          <t>-54,34; 4,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,09; -11,78</t>
+          <t>-64,06; -14,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,22; 2,67</t>
+          <t>-55,71; 1,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-95,98; -52,64</t>
+          <t>-95,17; -49,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,5; -8,92</t>
+          <t>-82,49; -7,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,19; -12,67</t>
+          <t>-71,83; 0,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,39; -21,44</t>
+          <t>-63,66; -19,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,8; -28,86</t>
+          <t>-66,37; -27,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,16; -18,34</t>
+          <t>-55,74; -11,11</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-3,02</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,2</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -2,1</t>
+          <t>-8,13; -2,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,05; -1,95</t>
+          <t>-7,85; -1,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 0,24</t>
+          <t>-6,22; 0,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,61</t>
+          <t>-2,01; 1,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,78</t>
+          <t>-2,36; 0,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,1</t>
+          <t>-0,31; 3,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,41</t>
+          <t>-3,63; -0,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,77; -0,66</t>
+          <t>-3,82; -0,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,24</t>
+          <t>-1,84; 1,45</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-37,41%</t>
+          <t>-42,02%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-9,05%</t>
+          <t>-4,53%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-84,93; -35,57</t>
+          <t>-85,38; -39,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-82,36; -33,39</t>
+          <t>-82,67; -31,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-65,73; 9,97</t>
+          <t>-65,21; 8,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-53,97; 106,68</t>
+          <t>-54,4; 123,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-68,88; 51,13</t>
+          <t>-66,52; 69,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 188,87</t>
+          <t>-12,57; 191,12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-65,57; -8,65</t>
+          <t>-67,42; -11,01</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-70,17; -20,96</t>
+          <t>-70,35; -21,07</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-39,49; 40,7</t>
+          <t>-34,36; 46,18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,69</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,11; -0,3</t>
+          <t>-3,17; -0,3</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,51</t>
+          <t>-1,82; 1,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,22</t>
+          <t>-2,46; 0,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; -0,41</t>
+          <t>-2,78; -0,42</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,78; -0,24</t>
+          <t>-2,86; -0,45</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,86</t>
+          <t>-1,87; 0,72</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,58</t>
+          <t>-2,58; -0,66</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,51; -0,4</t>
+          <t>-2,37; -0,32</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,39</t>
+          <t>-1,77; 0,29</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-65,84%</t>
+          <t>-64,89%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-16,53%</t>
+          <t>-20,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-24,68%</t>
+          <t>-26,04%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-76,43; -14,41</t>
+          <t>-76,72; -15,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-76,65; -9,93</t>
+          <t>-78,25; -13,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 36,43</t>
+          <t>-50,38; 32,83</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-78,4; -25,76</t>
+          <t>-78,65; -24,71</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-74,13; -17,23</t>
+          <t>-74,48; -12,82</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-53,67; 20,0</t>
+          <t>-54,38; 16,09</t>
         </is>
       </c>
     </row>
@@ -1930,29 +1930,29 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>-1,51</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>-1,48</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
           <t>-1,76</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-1,76</t>
-        </is>
-      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
           <t>-1,84</t>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>-0,94</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; -1,24</t>
+          <t>-2,83; -1,16</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,08; -1,39</t>
+          <t>-2,98; -1,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,75; -0,97</t>
+          <t>-2,38; -0,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,16; -0,88</t>
+          <t>-2,2; -0,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; -0,8</t>
+          <t>-2,15; -0,76</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,38</t>
+          <t>-0,99; 0,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; -1,16</t>
+          <t>-2,27; -1,19</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -1,33</t>
+          <t>-2,42; -1,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,63; -0,47</t>
+          <t>-1,53; -0,37</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-42,22%</t>
+          <t>-39,04%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-15,86%</t>
+          <t>-9,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-31,64%</t>
+          <t>-27,36%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-63,34; -32,55</t>
+          <t>-61,72; -30,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-65,7; -37,12</t>
+          <t>-64,5; -35,79</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,6; -25,91</t>
+          <t>-51,69; -20,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-69,08; -36,93</t>
+          <t>-69,98; -33,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-69,16; -32,83</t>
+          <t>-69,39; -32,62</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 16,88</t>
+          <t>-31,93; 17,31</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-60,51; -38,51</t>
+          <t>-61,05; -37,45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-63,64; -41,78</t>
+          <t>-63,66; -42,39</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-44,5; -15,72</t>
+          <t>-39,84; -11,74</t>
         </is>
       </c>
     </row>
